--- a/artfynd/A 40010-2025 artfynd.xlsx
+++ b/artfynd/A 40010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80557307</v>
+        <v>922203</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Sverige, Ång</t>
+          <t>Högnäsån, Högnäset, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533123.0329583033</v>
+        <v>533100</v>
       </c>
       <c r="R2" t="n">
-        <v>7141423.004281298</v>
+        <v>7141512</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>v sidan Högnäsån, tallskog, lavristyp. Skogen inte så gammal, dåligt med död ved. Tallskog på grusås intill bäcken, i övrigt blandskog, sumpskog i lägre partier. Skogen ca 130 år älsta ca180år. plockhugget.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,30 +762,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80554816</v>
+        <v>80557307</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra sverige, Ång</t>
+          <t>Norra Sverige, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533161.8338405304</v>
+        <v>533123</v>
       </c>
       <c r="R3" t="n">
-        <v>7141320.024016148</v>
+        <v>7141423</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -875,11 +869,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast hackspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,6 +890,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80554816</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra sverige, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533162</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7141320</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast hackspår</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40010-2025 artfynd.xlsx
+++ b/artfynd/A 40010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/922203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80557307</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80554816</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>